--- a/outputs/monitor_xlsx/20260324.xlsx
+++ b/outputs/monitor_xlsx/20260324.xlsx
@@ -544,10 +544,6 @@
           <t>-0.34%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-3.47%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.65%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+1.29%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+3.71%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.50%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+1.28%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>+3.06%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-1.12%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>-123.06億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-436.93億</t>
@@ -811,7 +774,6 @@
           <t>23.8億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>26.68億</t>
@@ -822,8 +784,6 @@
           <t>133.38億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>111.3%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>126.32%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>-204.11億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>10142口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>11511口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>28.09億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>2.75億</t>
@@ -1020,10 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1180,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2419,6 +2362,112 @@
       <c r="W22" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>8190</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E23" t="n">
+        <v>548</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>98</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-35</v>
+      </c>
+      <c r="J23" t="n">
+        <v>38</v>
+      </c>
+      <c r="K23" t="n">
+        <v>279</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1319</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-8959</v>
+      </c>
+      <c r="N23" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1480</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4243</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-309</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1474</v>
+      </c>
+      <c r="H24" t="n">
+        <v>823</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2330</v>
+      </c>
+      <c r="J24" t="n">
+        <v>241</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2732</v>
+      </c>
+      <c r="L24" t="n">
+        <v>12204</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-106311</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260324.xlsx
+++ b/outputs/monitor_xlsx/20260324.xlsx
@@ -544,6 +544,10 @@
           <t>-0.34%</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,14 +562,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>317.02</t>
+          <t>312.74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-3.47%</t>
-        </is>
-      </c>
+          <t>-1.35%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,6 +596,10 @@
           <t>+0.65%</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -610,6 +622,10 @@
           <t>+1.29%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -624,14 +640,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4567.7$</t>
+          <t>4399.3$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+3.71%</t>
-        </is>
-      </c>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -654,6 +674,10 @@
           <t>-0.50%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -676,6 +700,10 @@
           <t>+1.28%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +726,10 @@
           <t>+3.06%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -712,14 +744,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>87.14$</t>
+          <t>92.35$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-1.12%</t>
-        </is>
-      </c>
+          <t>+4.79%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -737,6 +773,7 @@
           <t>-123.06億</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-436.93億</t>
@@ -774,6 +811,7 @@
           <t>23.8億</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>26.68億</t>
@@ -784,6 +822,8 @@
           <t>133.38億</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -798,14 +838,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>111.3%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>126.32%</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -823,6 +867,11 @@
           <t>-204.11億</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,11 +889,15 @@
           <t>10142口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>11511口</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -862,6 +915,7 @@
           <t>28.09億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>2.75億</t>
@@ -966,6 +1020,10 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1087,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1105,14 +1163,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1122,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1201,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1286,12 +1337,7 @@
       <c r="N4" t="n">
         <v>-4520677</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1346,12 +1392,7 @@
       <c r="N5" t="n">
         <v>-78864</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1406,12 +1447,7 @@
       <c r="N6" t="n">
         <v>-649385</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1466,12 +1502,7 @@
       <c r="N7" t="n">
         <v>-6483116</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1480,12 +1511,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1494,44 +1525,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>99.5</v>
+        <v>1535</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>-7.44</v>
+        <v>-1.92</v>
       </c>
       <c r="F8" t="n">
-        <v>226815</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>-14643</v>
+        <v>4590</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>-139232</v>
+        <v>48</v>
       </c>
       <c r="I8" t="n">
-        <v>-17506</v>
+        <v>206</v>
       </c>
       <c r="J8" t="n">
-        <v>61099</v>
+        <v>551</v>
       </c>
       <c r="K8" t="n">
-        <v>8843</v>
+        <v>214</v>
       </c>
       <c r="L8" t="n">
-        <v>126568</v>
+        <v>2232</v>
       </c>
       <c r="M8" t="n">
-        <v>533384</v>
+        <v>9086</v>
       </c>
       <c r="N8" t="n">
-        <v>-1125000</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140185</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1540,12 +1566,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,44 +1580,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2685</v>
+        <v>1480</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-3.94</v>
+        <v>-2.63</v>
       </c>
       <c r="F9" t="n">
-        <v>3977</v>
+        <v>4243</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-495</v>
+        <v>-309</v>
       </c>
       <c r="H9" t="n">
-        <v>-559</v>
+        <v>-1165</v>
       </c>
       <c r="I9" t="n">
-        <v>77</v>
+        <v>823</v>
       </c>
       <c r="J9" t="n">
-        <v>63</v>
+        <v>1506</v>
       </c>
       <c r="K9" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="L9" t="n">
-        <v>2052</v>
+        <v>2732</v>
       </c>
       <c r="M9" t="n">
-        <v>7747</v>
+        <v>12936</v>
       </c>
       <c r="N9" t="n">
-        <v>-89580</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106311</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1600,12 +1621,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1614,44 +1635,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3110</v>
+        <v>2685</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>-2.51</v>
+        <v>-3.94</v>
       </c>
       <c r="F10" t="n">
-        <v>1439</v>
+        <v>3977</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-308</v>
+        <v>-495</v>
       </c>
       <c r="H10" t="n">
-        <v>464</v>
+        <v>-559</v>
       </c>
       <c r="I10" t="n">
-        <v>-6</v>
+        <v>77</v>
       </c>
       <c r="J10" t="n">
-        <v>-256</v>
+        <v>63</v>
       </c>
       <c r="K10" t="n">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="L10" t="n">
-        <v>5944</v>
+        <v>2052</v>
       </c>
       <c r="M10" t="n">
-        <v>23256</v>
+        <v>7747</v>
       </c>
       <c r="N10" t="n">
-        <v>-19782</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89580</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1706,12 +1722,7 @@
       <c r="N11" t="n">
         <v>-19518</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1720,58 +1731,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1400</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>-5.41</v>
+        <v>8190</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>3.87</v>
       </c>
       <c r="F12" t="n">
-        <v>679</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>19</v>
+        <v>548</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-35</v>
       </c>
       <c r="H12" t="n">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="I12" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="J12" t="n">
-        <v>126</v>
+        <v>-23</v>
       </c>
       <c r="K12" t="n">
-        <v>-76</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>-85</v>
+        <v>279</v>
       </c>
       <c r="M12" t="n">
-        <v>-421</v>
+        <v>1040</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8959</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1780,12 +1786,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1794,44 +1800,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>387</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1.84</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>15656</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>801</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>-1768</v>
+        <v>266</v>
       </c>
       <c r="I13" t="n">
-        <v>240</v>
+        <v>-4</v>
       </c>
       <c r="J13" t="n">
-        <v>-1338</v>
+        <v>126</v>
       </c>
       <c r="K13" t="n">
-        <v>-10</v>
+        <v>-76</v>
       </c>
       <c r="L13" t="n">
-        <v>-86</v>
+        <v>-85</v>
       </c>
       <c r="M13" t="n">
-        <v>1580</v>
+        <v>-421</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1840,12 +1841,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1854,44 +1855,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1285</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>-2.65</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>387</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>2</v>
+        <v>801</v>
       </c>
       <c r="H14" t="n">
-        <v>-75</v>
+        <v>-1768</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>240</v>
       </c>
       <c r="J14" t="n">
-        <v>-1</v>
+        <v>-1338</v>
       </c>
       <c r="K14" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="L14" t="n">
-        <v>-43</v>
+        <v>-86</v>
       </c>
       <c r="M14" t="n">
-        <v>-46</v>
+        <v>1580</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1900,58 +1896,53 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1535</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>-1.92</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>4590</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>8</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-1759</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>-1223</v>
       </c>
       <c r="I15" t="n">
-        <v>206</v>
+        <v>1439</v>
       </c>
       <c r="J15" t="n">
-        <v>551</v>
+        <v>2318</v>
       </c>
       <c r="K15" t="n">
-        <v>214</v>
+        <v>-71</v>
       </c>
       <c r="L15" t="n">
-        <v>2232</v>
+        <v>236</v>
       </c>
       <c r="M15" t="n">
-        <v>9086</v>
+        <v>874</v>
       </c>
       <c r="N15" t="n">
-        <v>-140185</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1960,12 +1951,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1974,500 +1965,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>839</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>2.19</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>1351</v>
+        <v>904</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="H16" t="n">
-        <v>-168</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>70</v>
+        <v>-6</v>
       </c>
       <c r="K16" t="n">
-        <v>28</v>
+        <v>-29</v>
       </c>
       <c r="L16" t="n">
-        <v>-240</v>
+        <v>-125</v>
       </c>
       <c r="M16" t="n">
-        <v>-481</v>
+        <v>62</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>935</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4489</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>322</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-3507</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-24</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-516</v>
-      </c>
-      <c r="K17" t="n">
-        <v>203</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2958</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11558</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-47646</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>均豪</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1035</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>134</v>
-      </c>
-      <c r="H18" t="n">
-        <v>26</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-29</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-125</v>
-      </c>
-      <c r="M18" t="n">
-        <v>62</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>869</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F19" t="n">
-        <v>12939</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>-1759</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-1223</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1439</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2318</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-71</v>
-      </c>
-      <c r="L19" t="n">
-        <v>236</v>
-      </c>
-      <c r="M19" t="n">
-        <v>874</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>234.5</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="F20" t="n">
-        <v>3269</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>350</v>
-      </c>
-      <c r="H20" t="n">
-        <v>804</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-11</v>
-      </c>
-      <c r="K20" t="n">
-        <v>193</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6077</v>
-      </c>
-      <c r="M20" t="n">
-        <v>27335</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-59054</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>華夏</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>-3.79</v>
-      </c>
-      <c r="F21" t="n">
-        <v>51442</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>-182</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2295</v>
-      </c>
-      <c r="J21" t="n">
-        <v>200</v>
-      </c>
-      <c r="K21" t="n">
-        <v>89</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7142</v>
-      </c>
-      <c r="M21" t="n">
-        <v>30529</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-145262</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>20</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F22" t="n">
-        <v>47856</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>2167</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3773</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>63</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7576</v>
-      </c>
-      <c r="M22" t="n">
-        <v>31753</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-99396</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>8190</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="E23" t="n">
-        <v>548</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G23" t="n">
-        <v>98</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-12</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-35</v>
-      </c>
-      <c r="J23" t="n">
-        <v>38</v>
-      </c>
-      <c r="K23" t="n">
-        <v>279</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1319</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-8959</v>
-      </c>
-      <c r="N23" t="n">
-        <v>37.51</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1480</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4243</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>-309</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-1474</v>
-      </c>
-      <c r="H24" t="n">
-        <v>823</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2330</v>
-      </c>
-      <c r="J24" t="n">
-        <v>241</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2732</v>
-      </c>
-      <c r="L24" t="n">
-        <v>12204</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-106311</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260324.xlsx
+++ b/outputs/monitor_xlsx/20260324.xlsx
@@ -544,10 +544,6 @@
           <t>-0.34%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-1.35%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.65%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+1.29%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-0.11%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.50%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+1.28%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>+3.06%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>+4.79%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>-123.06億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-436.93億</t>
@@ -811,7 +774,6 @@
           <t>23.8億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>26.68億</t>
@@ -822,8 +784,6 @@
           <t>133.38億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>126.32%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>-204.11億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>10142口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>11511口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>28.09億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>2.75億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1998,6 +1942,45 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>317</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="E17" t="n">
+        <v>836</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-215</v>
+      </c>
+      <c r="I17" t="n">
+        <v>30</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8104</v>
+      </c>
+      <c r="L17" t="n">
+        <v>42261</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22122</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.09</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260324.xlsx
+++ b/outputs/monitor_xlsx/20260324.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,20 +1250,23 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>90466</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-21894</v>
       </c>
       <c r="H4" t="n">
-        <v>-213668</v>
+        <v>-235562</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>5800</v>
@@ -1276,11 +1278,14 @@
         <v>13782</v>
       </c>
       <c r="M4" t="n">
-        <v>52947</v>
+        <v>66729</v>
       </c>
       <c r="N4" t="n">
         <v>-4520677</v>
       </c>
+      <c r="O4" t="n">
+        <v>-3.42</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1303,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="7" t="n">
         <v>881</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>-1.01</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>2449</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>-217</v>
       </c>
       <c r="H5" t="n">
-        <v>-457</v>
+        <v>-674</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="K5" t="n">
         <v>116</v>
@@ -1331,11 +1336,14 @@
         <v>2890</v>
       </c>
       <c r="M5" t="n">
-        <v>11618</v>
+        <v>14508</v>
       </c>
       <c r="N5" t="n">
         <v>-78864</v>
       </c>
+      <c r="O5" t="n">
+        <v>-6.29</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1358,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1415</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0.35</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>13206</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>2115</v>
       </c>
       <c r="H6" t="n">
-        <v>2312</v>
+        <v>4428</v>
       </c>
       <c r="I6" t="n">
         <v>264</v>
       </c>
       <c r="J6" t="n">
-        <v>-169</v>
+        <v>95</v>
       </c>
       <c r="K6" t="n">
         <v>414</v>
@@ -1386,11 +1394,14 @@
         <v>5368</v>
       </c>
       <c r="M6" t="n">
-        <v>21641</v>
+        <v>27009</v>
       </c>
       <c r="N6" t="n">
         <v>-649385</v>
       </c>
+      <c r="O6" t="n">
+        <v>2.5</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1419,20 +1430,20 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>30569</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>-5178</v>
       </c>
       <c r="H7" t="n">
-        <v>-44491</v>
+        <v>-49669</v>
       </c>
       <c r="I7" t="n">
         <v>691</v>
       </c>
       <c r="J7" t="n">
-        <v>-2412</v>
+        <v>-1721</v>
       </c>
       <c r="K7" t="n">
         <v>824</v>
@@ -1441,11 +1452,14 @@
         <v>26367</v>
       </c>
       <c r="M7" t="n">
-        <v>103644</v>
+        <v>130011</v>
       </c>
       <c r="N7" t="n">
         <v>-6483116</v>
       </c>
+      <c r="O7" t="n">
+        <v>-4.28</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1468,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>1535</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>-1.92</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>4590</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I8" t="n">
         <v>206</v>
       </c>
       <c r="J8" t="n">
-        <v>551</v>
+        <v>757</v>
       </c>
       <c r="K8" t="n">
         <v>214</v>
@@ -1496,11 +1510,14 @@
         <v>2232</v>
       </c>
       <c r="M8" t="n">
-        <v>9086</v>
+        <v>11318</v>
       </c>
       <c r="N8" t="n">
         <v>-140185</v>
       </c>
+      <c r="O8" t="n">
+        <v>4.96</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1523,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1480</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>-2.63</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>4243</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-309</v>
       </c>
       <c r="H9" t="n">
-        <v>-1165</v>
+        <v>-1474</v>
       </c>
       <c r="I9" t="n">
         <v>823</v>
       </c>
       <c r="J9" t="n">
-        <v>1506</v>
+        <v>2330</v>
       </c>
       <c r="K9" t="n">
         <v>241</v>
@@ -1551,11 +1568,14 @@
         <v>2732</v>
       </c>
       <c r="M9" t="n">
-        <v>12936</v>
+        <v>15668</v>
       </c>
       <c r="N9" t="n">
         <v>-106311</v>
       </c>
+      <c r="O9" t="n">
+        <v>3.23</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1578,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2685</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>-3.94</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>3977</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>-495</v>
       </c>
       <c r="H10" t="n">
-        <v>-559</v>
+        <v>-1053</v>
       </c>
       <c r="I10" t="n">
         <v>77</v>
       </c>
       <c r="J10" t="n">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="K10" t="n">
         <v>247</v>
@@ -1606,11 +1626,14 @@
         <v>2052</v>
       </c>
       <c r="M10" t="n">
-        <v>7747</v>
+        <v>9799</v>
       </c>
       <c r="N10" t="n">
         <v>-89580</v>
       </c>
+      <c r="O10" t="n">
+        <v>6.86</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1633,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>1935</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4.59</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>3749</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>-280</v>
       </c>
       <c r="H11" t="n">
-        <v>-304</v>
+        <v>-583</v>
       </c>
       <c r="I11" t="n">
         <v>582</v>
       </c>
       <c r="J11" t="n">
-        <v>285</v>
+        <v>868</v>
       </c>
       <c r="K11" t="n">
         <v>120</v>
@@ -1661,11 +1684,14 @@
         <v>4174</v>
       </c>
       <c r="M11" t="n">
-        <v>16563</v>
+        <v>20737</v>
       </c>
       <c r="N11" t="n">
         <v>-19518</v>
       </c>
+      <c r="O11" t="n">
+        <v>0.38</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1688,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>8190</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>3.87</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>548</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>-35</v>
       </c>
       <c r="H12" t="n">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="I12" t="n">
         <v>-12</v>
       </c>
       <c r="J12" t="n">
-        <v>-23</v>
+        <v>-35</v>
       </c>
       <c r="K12" t="n">
         <v>38</v>
@@ -1716,11 +1742,14 @@
         <v>279</v>
       </c>
       <c r="M12" t="n">
-        <v>1040</v>
+        <v>1319</v>
       </c>
       <c r="N12" t="n">
         <v>-8959</v>
       </c>
+      <c r="O12" t="n">
+        <v>37.51</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1743,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="I13" t="n">
         <v>-4</v>
       </c>
       <c r="J13" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K13" t="n">
         <v>-76</v>
@@ -1771,11 +1800,14 @@
         <v>-85</v>
       </c>
       <c r="M13" t="n">
-        <v>-421</v>
+        <v>-506</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1798,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>801</v>
       </c>
       <c r="H14" t="n">
-        <v>-1768</v>
+        <v>-966</v>
       </c>
       <c r="I14" t="n">
         <v>240</v>
       </c>
       <c r="J14" t="n">
-        <v>-1338</v>
+        <v>-1098</v>
       </c>
       <c r="K14" t="n">
         <v>-10</v>
@@ -1826,11 +1858,14 @@
         <v>-86</v>
       </c>
       <c r="M14" t="n">
-        <v>1580</v>
+        <v>1494</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1853,26 +1888,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>-1759</v>
       </c>
       <c r="H15" t="n">
-        <v>-1223</v>
+        <v>-2982</v>
       </c>
       <c r="I15" t="n">
         <v>1439</v>
       </c>
       <c r="J15" t="n">
-        <v>2318</v>
+        <v>3757</v>
       </c>
       <c r="K15" t="n">
         <v>-71</v>
@@ -1881,11 +1916,14 @@
         <v>236</v>
       </c>
       <c r="M15" t="n">
-        <v>874</v>
+        <v>1110</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,20 +1946,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>134</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>160</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-6</v>
@@ -1933,11 +1974,14 @@
         <v>-125</v>
       </c>
       <c r="M16" t="n">
-        <v>62</v>
+        <v>-63</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1955,32 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>317</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>-2.46</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>836</v>
       </c>
-      <c r="G17" t="n">
-        <v>-215</v>
+      <c r="G17" s="6" t="n">
+        <v>-66</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-281</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>30</v>
       </c>
       <c r="K17" t="n">
+        <v>28</v>
+      </c>
+      <c r="L17" t="n">
         <v>8104</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>42261</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-22122</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.09</v>
+      <c r="O17" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260324.xlsx
+++ b/outputs/monitor_xlsx/20260324.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>-0.12</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1620</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5766</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-4356</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-129</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-716</v>
+      </c>
+      <c r="K18" t="n">
+        <v>215</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6120</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30278</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400976</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-6.36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>460</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10317</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10497</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1465</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-640</v>
+      </c>
+      <c r="K19" t="n">
+        <v>733</v>
+      </c>
+      <c r="L19" t="n">
+        <v>32033</v>
+      </c>
+      <c r="M19" t="n">
+        <v>168601</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393882</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-5.51</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>491</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>30733</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-2398</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-4379</v>
+      </c>
+      <c r="I20" t="n">
+        <v>384</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1291</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2151</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10232</v>
+      </c>
+      <c r="M20" t="n">
+        <v>52125</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161274</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-2.15</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
